--- a/PP1-Collection_Database.xlsx
+++ b/PP1-Collection_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lanmat\Documents\Creativ-up\Activités\2.Projets pilotes - WP4\Projet Pilote 1\2Développement\Collections for database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{F149F829-0908-4FFE-975B-3A0B46973071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633AE702-566C-4ECE-AEE3-72A626F98FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="938">
   <si>
     <t>Museum ID</t>
   </si>
@@ -311,10 +311,6 @@
     <t>Signe de reconnaissance, billet de papier, ruban, enfant déposé, bons soins, bébé</t>
   </si>
   <si>
-    <t>Signes de reconnaissance : images de piété, assignats, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son
-identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Cette collection a été léguée par les hospices civils de Mons.</t>
-  </si>
-  <si>
     <t>MAR-BVM-7-2022.0.23</t>
   </si>
   <si>
@@ -634,9 +630,6 @@
   </si>
   <si>
     <t>MAR-BVM-7-2022.0.62</t>
-  </si>
-  <si>
-    <t>JL.2022.0.65</t>
   </si>
   <si>
     <t>JL.2022.0.67</t>
@@ -2064,9 +2057,6 @@
     <t>On désire que cet enfant s’appelle Gustave Joseph persoiens ( ?) que l’on veuille se souvenir la ou qu’on la placé le 27 juillet 1816.</t>
   </si>
   <si>
-    <t>Moitié d’avis de décès d’un certain Nicolas De Laroche qui a servi comme signe de reconnaissance pour un enfant déposé à l’hospice de Mons en 1830.</t>
-  </si>
-  <si>
     <t>Moitié découpée d’une gravure représentant la Sainte Famille et qui loue dans le texte Joseph, Joachim, Anna et Maria ainsi que le bonheur de vivre dans une famille.</t>
   </si>
   <si>
@@ -3010,6 +3000,69 @@
   </si>
   <si>
     <t>Cette carte à jouer de la première moitié du XIXe siècle a été découpée intentionnellement pour servir de signe de reconnaissance. Les signes de reconnaissance sont le plus souvent des images pieuses, des rubans, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant abandonné, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Ces signes de reconnaissance ont été laissés à des nourrissons déposés à l'Hospice civil de Mons et leur présence indique clairement que l'abandon a été fait à contrecoeur mais que les parents ont l'espoir de venir récupérer l'enfant un jour. Le choix d'une carte à jouer comme signe de reconnaissance, un objet banal du quotidien, témoigne très probablement de la situation économique délicate des parents et laisse deviner la raison de l'abandon. Au verso de la carte, les parents ont inscrits le prénom souhaité et la date de naissance : Victoire, 13 mars.</t>
+  </si>
+  <si>
+    <t>Cette carte à jouer de la première moitié du XIXe siècle a été découpée en deux intentionnellement pour servir de signe de reconnaissance. Les signes de reconnaissance sont le plus souvent des images pieuses, des rubans, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant abandonné, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Ces signes de reconnaissance ont été laissés à des nourrissons déposés à l'Hospice civil de Mons et leur présence indique clairement que l'abandon a été fait à contrecoeur mais que les parents ont l'espoir de venir récupérer l'enfant un jour. Le choix d'une carte à jouer comme signe de reconnaissance, un objet banal du quotidien, témoigne très probablement de la situation économique délicate des parents et laisse deviner la raison de l'abandon. Au revers de la carte, on peut lire un mot des parents qui avaient choisi un prénom pour leur fille, Marie-Joseph-Philippine, et l'avaient déjà batpisée.</t>
+  </si>
+  <si>
+    <t>Cette gravure représentant un jeune christ portant sa croix est un signe de reconnaissance qui accompagnait un nouveau-né laissé à l'hospice civil de Mons. Les signes de reconnaissances sont des objets laissés avec un nourrisson abandonné auprès d'un couvent ou d'un hospice qui permettent d'identifier l'enfant dans le cas où la mère voulait venir le reprendrequand sa situation lui permettrait. Souvent, il s'agit d'images de piété, de morceau de textile ou de cartes à jouer coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Ici, la gravure est entière mais au verso, on trouve un message touchant de la mère : "Baptisé, je vous prie de bien le placer je vous serai reconnaissant" et en bas figure une écriture ajoutée d'un prénom et de l'année : Charles, an 10. Ce qui correspond à l'année 1802.</t>
+  </si>
+  <si>
+    <t>Cette moitié de gravure représentant le portrait d'une jeune femme a été coupée en deux volontairement, il s'agit d'un des nombreux signes de reconnaissance conservés dans les collections de la Ville de Mons et héritée de l'hospice civil de Mons. L'hospice recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper, Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, on découvre un message touchant rédigé par un des parents avec la date de l'abandon :  le 27 avril 1802.</t>
+  </si>
+  <si>
+    <t>Cette gravure coupée en deux représente Saint-Martin et a servi de signe de reconnaissance. L'hospice Civil de Mons, anciennement couvent, recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, on découvre un message touchant rédigé par un des parents précisant le souhait du prénom pour l'enfant et la raison du choix  : "Ayez la bonté je vous prie de lui donner le nom d'Éloi puisqu'il est venu ce jour là"</t>
+  </si>
+  <si>
+    <t>Cette image a été coupée en deux de façon irrégulière pour servir de signe de reconnaissance, tel un puzzle, la partie supérieur peut venir s'y emboiter.  Sur le recto, on peut lire le nom d'Andreas et au verso un message rédigé par les parents du nouveau-né déposé avec ce signe à l'hospice civil de Mons entre 1800 et 1850 . Cette image est un fragment du signe de reconnaissance, l'autre fragment sensé s'emboiter au premier a été conservé par les parents au moment de l'abandon. Les signes de reconnaissance comme celui-ci étaient très souvent composés de deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. La présence de signes de reconnaissance sur le nourrisson abandonné indique que les parents se résignaient à l'abandon à contrecoeur, avec l'espoir de pouvoir récupérer l'enfant plus tard, dans des temps meilleurs. La forme des signes de reconnaissance donne aussi un indice sur la situation des parents; au plus l'objet est simple et issu du quotidien, au plus la probabilité d'un abandon par manque de moyens financiers est grande. Au verso, les parents précisent le prénom souhaité pour l'enfant : Gabriel-Alexandre.</t>
+  </si>
+  <si>
+    <t>La découpe en zig-zag dans ce dessin délicat représentant des fleurs colorées indique que l'image a servi de signe de reconnaissance, tel un puzzle, l'autre moitié doit venir s'y emboiter. Au verso, un prénom : Pauline . L'autre fragment a été conservé par les parents au moment de l'abandon de leur nourrisson aux bons soins du couvent. Les signes de reconnaissance comme celui-ci étaient très souvent composés de deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. La présence de signes de reconnaissance sur le nourrisson abandonné indique que les parents se résignaient à l'abandon à contrecoeur, avec l'espoir de pouvoir récupérer l'enfant plus tard, dans des temps meilleurs. La forme des signes de reconnaissance donne aussi un indice sur la situation des parents; au plus l'objet est simple et issu du quotidien, au plus la probabilité d'un abandon par manque de moyens financiers est grande.</t>
+  </si>
+  <si>
+    <t>Cette gravure du portrait d'un martyre coupée en deux a servi de signe de reconnaissance. L'hospice Civil de Mons, anciennement couvent, recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, on découvre un message touchant rédigé par un des parents précisant le souhait du prénom pour l'enfant : "Il faut l'appeler Louis"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette gravure du christ coupée en deux dans la longueur a servi de signe de reconnaissance. L'hospice Civil de Mons, anciennement couvent, recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, on découvre un message touchant rédigé par un des parents précisant le souhait du prénom pour l'enfant : "Cette enfant est baptisée. Elle se nomme Joséphine. Monsieur je vous prie d’en avoir bon soins, ce n’est pas pour longtemps", Au travers de ce message, on comprend que l'abandon est fait à contrecoeur et que les parents nourrissent bien l'espoir de pouvoir venir récupérer leur enfant un jour. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce portrait au décor très coloré a été coupé en deux volontairement, Il s'agit d'un signe de reconnaissance qui se trouvait avec de nombreux autres dans les archives de l'Hospice Civil de Mons. L'hospice Civil de Mons, dénommé  couvent avant la révolution française, recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, on peut lire un prénom: Adélaïde Bouleau et l'année de l'abandon : an 10 (qui correspond à 1802 dans notre calendrier grégorien). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette gravure a été coupée en deux de façon irrégulière volontairement pour servir de signe de reconnaissance. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné déposé de façon anonyme à l'Hospice Civil de Mons par les parents dans l'incapacité de s'en occuper. Au revers, on découvre un message touchant rédigé par un des parents :" Je prie les administrateurs d’en prendre soin. Ce n'est pas pour longtemps". Au travers de ce message, on comprend que l'abandon est fait à contrecoeur et que les parents nourrissent bien l'espoir de pouvoir venir récupérer leur enfant un jour. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette carte à jouer de la première moitié du XIXe siècle a été découpée a servi de signe de reconnaissance comme l'indique la découpe irrégulière et le message manuscrit. Les signes de reconnaissance sont le plus souvent des images pieuses, des rubans, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant abandonné, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. L'inscription sur la carte confirme la nature de l'objet, à savoir une marque de reconnaissance et le prénom souhaité pour l'enfant : " La remarque pour le reprendre Charles", Ces signes de reconnaissance conservés dans les collections communales de la Ville de Mons ont été laissés à des nourrissons déposés à l'Hospice civil de Mons et leur présence indique clairement que l'abandon a été fait à contrecoeur mais que les parents ont l'espoir de venir récupérer l'enfant un jour. Le choix d'une carte à jouer comme signe de reconnaissance, un objet banal du quotidien, témoigne très probablement de la situation économique délicate des parents et laisse deviner la raison de l'abandon. </t>
+  </si>
+  <si>
+    <t>Cette gravure avait été coupée en deux de façon irrégulière volontairement pour servir de signe de reconnaissance. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné déposé de façon anonyme à l'Hospice Civil de Mons par les parents dans l'incapacité de s'en occuper. Le fait que les deux fragments soient réunis indique que l'enfant déposé a été récupéré, ceci est d'ailleurs confirmé par l'inscription au verso : "Joseph Gabriel Custot. Réclamé et repris par la mère le 16 avril 1807"</t>
+  </si>
+  <si>
+    <t>Ce dessin représentant un bouquet  accompagné d'un dicton :"Ce coeur de Jésus pour présent, Vous est offert a tout moment" est un signe de reconnaissance.  Les signes de reconnaissance sont des objets composés de deux fragments: l'un est attaché aux langes de l'enfant déposé, l'autre fragment a été conservé par les parents au moment de l'abandon de leur nourrisson aux bons soins du couvent. La mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, présentait le fragment correspondant à celui que portait l'abandonné. L'enfant déposé avec ce signe-ci a donc été réclamé. La présence de signes de reconnaissance sur le nourrisson abandonné indique que les parents se résignaient à l'abandon à contrecoeur, avec l'espoir de pouvoir récupérer l'enfant plus tard, dans des temps meilleurs. La forme des signes de reconnaissance donne aussi un indice sur la situation des parents; au plus l'objet est simple et issu du quotidien, au plus la probabilité d'un abandon par manque de moyens financiers est grande. Ici, le choix de la devise sur le dessin n'est sans doute pas faite au hasard et indique ces objets peuvent parfois prendre le statut de présent laissé au nouveau-né,</t>
+  </si>
+  <si>
+    <t>Cette gravure avec des rehauts de couleurs représentant Saint-Elisabeth avait été coupée en deux pour servir de signe de reconnaissance. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné déposé de façon anonyme à l'Hospice Civil de Mons par les parents dans l'incapacité de s'en occuper. Le fait que les deux fragments soient réunis indique que la mère est  venue récupérer l'enfant, malheureusement sur un des fragments, on peut lire que l'enfant est décédé le 28 mars 1806.</t>
+  </si>
+  <si>
+    <t>Cette page de livre avait été coupée en deux de façon irrégulière volontairement pour servir de signe de reconnaissance. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné déposé de façon anonyme à l'Hospice Civil de Mons. Sur un des fragments on peut lire le prénom atrtiué au nourrisson et la date de l'abandon :"Victor le 2 juillet", Le fait que les deux fragments soient réunis indique que l'enfant déposé a été récupéré, et confirme que les parents laissant ces marques de reconnaissances ont bien l'espoir de venir récupérer leur enfant en des temps meilleurs,</t>
+  </si>
+  <si>
+    <t>Ce petit bonnet fleuri avec broderie accompagnait un nourrisson déposé de façon anonyme à l'Hospice Civil de Mons. Les signes de reconnaissance sont généralement des images pieuses, une feuille découpée de façon irrégulière, un ruban, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné.La présence d'un signe de reconnaissance indique clairement que c'était souvent à contrecoeur que les parents se résignaient à l'abandon, suite à une situation économique trop défavorable par exemple, mais qu'ils avaient l'espoir de récupérer l'enfant dans des temps meilleurs. Ce petit bonnet a été laissé comme marque avec l'enfant sans doute pour son aspect reconnaissable et spécifique. La forme des signes de reconnaissance donne aussi un indice sur la situation des parents; au plus l'objet est simple et issu du quotidien, au plus la probabilité d'un abandon par manque de moyens financiers est grande. Le signe de reconnaissance laissé au nourrisson peut aussi être interprété comme une marque d'affection et un présent laissé par les parents à leur enfant, d'ou le soin apporté dans certains cas au choix des effets laissés avec l'abandonné.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce petit bracelet avec des perles de verre bleu a été laissé comme signe de reconnaissance sur un des enfants déposés à l'hospice civil de Mons. Ces objets distinctifs laissés auprès du nouveau né abandonné anonymement devaient  servir à l'identification du bébé au cas où la mère voulait le reprendre et justifier son identité. Les signes de reconnaissance sont le plus souvent des objets aisément reconnaissables laissés à l'enfant, comme par exemple une image pieuse, une carte à jouer, un ruban coupé en deux fragments:  l'un attaché à l'enfant, l'autre conservé par le parent qui le présentait pour justifier la reprise de l'enfant. Les signes comme celui-ci représentent à la fois un présent laissé au nouveau et témoignent d'une marque d'affection qui indique clairement que l'abandon s'est fait à contrecoeur. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette lettre manuscrite accompagnait une petite fille née le 25 mai 1812 déposée à l'hospice civil de Mons de façon anonyme avec une image qui devait servir de marque de reconnaissance. les signes de reconnaissance sont des objets variés: images de piété, assignats, cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au travers de la lettre, on apprend les motivations pour l'abandon du nouveau-né: il s'agit du fruit d'une union illégitime qui doit rester cachée aux parents de la jeune mère, cependant, dans son message, la mère demande de façon touchante de placer la petite si possible de sorte qu'elle puisse tout de même revoir l'enfant à l'insu de ses parents. Elle mentionne aussi que son confesseur jouera l'intermédiare avec "le bureau des bienfaisances" pour lui permettre de savoir où sera placé l'enfant. </t>
+  </si>
+  <si>
+    <t>Cette gravure coupée en deux représente Saint-Luc et a servi de signe de reconnaissance. L'hospice Civil de Mons, parfois mentionné comme "Bureau des bienfaisances", recueillait les nouveaux-nés déposés de façon anonyme par les parents dans l'incapacité de s'en occuper. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l'enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné. Au revers, un message précise qu'il s'agit d'un garçon pas encore baptisé et la date de naissance ou d'abandon: le 4 février,</t>
+  </si>
+  <si>
+    <t>Ce chapelet a été laissé comme signe de reconnaissance sur un des enfants déposés à l'hospice civil de Mons. Ces objets distinctifs laissés auprès du nouveau né abandonné anonymement devaient  servir à l'identification du bébé au cas où la mère voulait le reprendre et justifier son identité. Les signes de reconnaissance sont le plus souvent des objets aisément reconnaissables laissés à l'enfant, comme par exemple une image pieuse, une carte à jouer, un ruban coupé en deux fragments:  l'un attaché à l'enfant, l'autre conservé par le parent qui le présentait pour justifier la reprise de l'enfant. Les signes comme celui-ci représentent à la fois un présent laissé au nouveau et témoignent d'une marque d'affection qui indique clairement que l'abandon s'est fait à contrecoeur. Ce signe de reconnaissance était accompagné d'un billet sur lequel on peut lire : "Ce petit garçon est venu au monde le 24 aout 1818 a trois heures de l’après-midi",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette gravure représentant Saint-Anne a été coupée en deux de façon irrégulière volontairement pour servir de signe de reconnaissance. Les signes de reconnaissance sont des images pieuses, des pages de livres, des cartes à jouer, etc., coupés en deux fragments : l'un des fragments était attaché aux langes de l'enfant, l'autre était conservé par la mère, pour le cas où elle voulait reprendre l' enfant et justifier son identité, par la présentation du fragment correspondant à celui que portait l'abandonné déposé de façon anonyme à l'Hospice Civil de Mons dans le cas présent. Tel un puzzle, le deuxième fragment vient s'emboiter au premier.  Cette marque est accompagnée d'un billet de la mère qui précise quelques souhaits :  elle voudrait qu'il soit placé très proche de la ville, de lui choisir une bonne nourrice, de le baptiser et de lui donner le prénom de Narcisse. La présence de signe de reconnaissance et de ce message indique donc clairement que l'abandon se faisait à contrecoeur et que les parents n'étaient pas du tout insensibles à l'avenir de l'abandonné. </t>
   </si>
 </sst>
 </file>
@@ -3052,7 +3105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3073,19 +3126,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3143,7 +3184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3163,18 +3204,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3211,12 +3240,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3515,7 +3557,7 @@
     <col min="9" max="9" width="19.44140625" customWidth="1"/>
     <col min="10" max="10" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="19.77734375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="31.6640625" customWidth="1"/>
+    <col min="13" max="13" width="31.6640625" style="27" customWidth="1"/>
     <col min="14" max="14" width="27.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3552,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="21" t="s">
         <v>18</v>
       </c>
       <c r="N1" s="4" t="s">
@@ -3582,10 +3624,10 @@
         <v>4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>6</v>
@@ -3594,16 +3636,16 @@
         <v>7</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="M2" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="M2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="9" t="s">
         <v>20</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="144" x14ac:dyDescent="0.3">
@@ -3614,34 +3656,34 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E3">
         <v>2016</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="M3" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="M3" s="23" t="s">
         <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="384.6" x14ac:dyDescent="0.3">
@@ -3652,37 +3694,37 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E4">
         <v>2015</v>
       </c>
       <c r="F4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="M4" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="M4" s="24" t="s">
         <v>30</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="372.6" x14ac:dyDescent="0.3">
@@ -3693,34 +3735,34 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E5">
         <v>2024</v>
       </c>
       <c r="F5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="H5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="M5" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="M5" s="24" t="s">
         <v>33</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="288" x14ac:dyDescent="0.3">
@@ -3731,34 +3773,34 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E6">
         <v>2015</v>
       </c>
       <c r="F6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>471</v>
+        <v>535</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>469</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="330" x14ac:dyDescent="0.3">
@@ -3778,28 +3820,28 @@
         <v>1896</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="L7" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="M7" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="M7" s="25" t="s">
         <v>37</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="409.2" x14ac:dyDescent="0.3">
@@ -3813,34 +3855,34 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E8">
         <v>1973</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H8" t="s">
         <v>36</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="M8" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="M8" s="25" t="s">
         <v>39</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="409.2" x14ac:dyDescent="0.3">
@@ -3863,25 +3905,25 @@
         <v>36</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="M9" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="M9" s="25" t="s">
         <v>42</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="145.19999999999999" x14ac:dyDescent="0.3">
@@ -3895,35 +3937,35 @@
         <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="O10" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
@@ -3937,35 +3979,35 @@
         <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="M11" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="M11" s="20" t="s">
         <v>48</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="144" x14ac:dyDescent="0.3">
@@ -3979,35 +4021,35 @@
         <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E12" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="M12" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="M12" s="20" t="s">
         <v>50</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -4021,7 +4063,7 @@
         <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
@@ -4030,25 +4072,25 @@
         <v>36</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="M13" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="M13" s="26" t="s">
         <v>53</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -4062,7 +4104,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="E14" t="s">
         <v>47</v>
@@ -4072,22 +4114,22 @@
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>497</v>
+        <v>539</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>495</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -4101,30 +4143,30 @@
         <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="M15" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="M15" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="14"/>
+      <c r="O15" s="10"/>
     </row>
     <row r="16" spans="1:15" ht="172.2" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -4137,35 +4179,35 @@
         <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E16" t="s">
         <v>58</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>59</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="M16" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="M16" s="26" t="s">
         <v>60</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="119.4" x14ac:dyDescent="0.3">
@@ -4179,35 +4221,35 @@
         <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="M17" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="M17" s="26" t="s">
         <v>63</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="145.80000000000001" x14ac:dyDescent="0.3">
@@ -4227,29 +4269,29 @@
         <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="M18" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="M18" s="26" t="s">
         <v>66</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -4263,35 +4305,35 @@
         <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M19" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="M19" s="26" t="s">
         <v>68</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="106.2" x14ac:dyDescent="0.3">
@@ -4305,35 +4347,35 @@
         <v>35</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E20" t="s">
         <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="M20" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="M20" s="26" t="s">
         <v>70</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -4347,7 +4389,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E21">
         <v>1803</v>
@@ -4362,24 +4404,24 @@
         <v>74</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>839</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M21" s="24" t="s">
-        <v>842</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O21" s="12" t="s">
+      <c r="O21" s="8" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4394,7 +4436,7 @@
         <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E22">
         <v>1802</v>
@@ -4412,19 +4454,19 @@
         <v>75</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>874</v>
+        <v>572</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>871</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>77</v>
+        <v>526</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -4432,43 +4474,43 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E23">
         <v>1834</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I23" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>842</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O23" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>845</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="360" x14ac:dyDescent="0.3">
@@ -4476,43 +4518,43 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
         <v>84</v>
-      </c>
-      <c r="F24" t="s">
-        <v>85</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>851</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M24" s="24" t="s">
-        <v>854</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -4520,37 +4562,37 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>843</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O25" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>846</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -4558,40 +4600,40 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E26" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="F26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>840</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>843</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
@@ -4599,40 +4641,40 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E27">
         <v>1834</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>841</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="M27" s="25" t="s">
-        <v>844</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -4640,40 +4682,40 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E28">
         <v>1813</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>844</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M28" s="25" t="s">
-        <v>847</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -4681,19 +4723,19 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E29">
         <v>1823</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G29" s="6">
         <v>45735</v>
@@ -4702,22 +4744,22 @@
         <v>74</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>845</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="O29" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="M29" s="25" t="s">
-        <v>848</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -4725,19 +4767,19 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E30">
         <v>1790</v>
       </c>
       <c r="F30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G30" s="6">
         <v>45867</v>
@@ -4746,22 +4788,22 @@
         <v>74</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>846</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O30" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="M30" s="25" t="s">
-        <v>849</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -4769,19 +4811,19 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E31">
         <v>1797</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G31" s="6">
         <v>45758</v>
@@ -4790,22 +4832,22 @@
         <v>74</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>847</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O31" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="M31" s="25" t="s">
-        <v>850</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="288" x14ac:dyDescent="0.3">
@@ -4813,19 +4855,19 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E32">
         <v>1804</v>
       </c>
       <c r="F32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G32" s="6">
         <v>45869</v>
@@ -4834,22 +4876,22 @@
         <v>74</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O32" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M32" s="25" t="s">
-        <v>851</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -4857,40 +4899,40 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E33">
         <v>1819</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>849</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O33" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="M33" s="25" t="s">
-        <v>852</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -4898,40 +4940,40 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
         <v>24</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E34">
         <v>1816</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>850</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="O34" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M34" s="25" t="s">
-        <v>853</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -4939,40 +4981,40 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E35">
         <v>1824</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>852</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="O35" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M35" s="25" t="s">
-        <v>855</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="230.4" x14ac:dyDescent="0.3">
@@ -4980,40 +5022,40 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I36" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>859</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O36" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M36" s="25" t="s">
-        <v>862</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -5021,40 +5063,40 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
         <v>24</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E37">
         <v>1826</v>
       </c>
       <c r="F37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>853</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O37" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="M37" s="25" t="s">
-        <v>856</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -5062,13 +5104,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E38">
         <v>1815</v>
@@ -5077,22 +5119,22 @@
         <v>74</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>855</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O38" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M38" s="25" t="s">
-        <v>858</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O38" s="12" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5100,40 +5142,40 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E39">
         <v>1834</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>854</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O39" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M39" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O39" s="12" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5141,13 +5183,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E40">
         <v>1823</v>
@@ -5159,22 +5201,22 @@
         <v>74</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>856</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M40" s="25" t="s">
-        <v>859</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5182,13 +5224,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E41">
         <v>1814</v>
@@ -5200,22 +5242,22 @@
         <v>74</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>857</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="O41" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M41" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -5223,19 +5265,19 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E42">
         <v>1818</v>
       </c>
       <c r="F42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G42" s="6">
         <v>45778</v>
@@ -5244,22 +5286,22 @@
         <v>74</v>
       </c>
       <c r="J42" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>858</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O42" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="M42" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O42" s="12" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -5267,43 +5309,43 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E43">
         <v>1814</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I43" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J43" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>860</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O43" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M43" s="25" t="s">
-        <v>863</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O43" s="12" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5311,13 +5353,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E44">
         <v>1816</v>
@@ -5326,22 +5368,22 @@
         <v>74</v>
       </c>
       <c r="J44" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>861</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O44" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="M44" s="25" t="s">
-        <v>864</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O44" s="12" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="360" x14ac:dyDescent="0.3">
@@ -5349,13 +5391,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E45">
         <v>1818</v>
@@ -5367,25 +5409,25 @@
         <v>74</v>
       </c>
       <c r="I45" t="s">
+        <v>163</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>862</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O45" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="M45" s="25" t="s">
-        <v>865</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O45" s="12" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -5393,40 +5435,40 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E46">
         <v>1817</v>
       </c>
       <c r="F46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J46" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>863</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O46" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M46" s="25" t="s">
-        <v>866</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O46" s="12" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -5434,40 +5476,40 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C47" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="M47" s="20" t="s">
+        <v>864</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O47" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="M47" s="25" t="s">
-        <v>867</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="O47" s="12" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -5475,40 +5517,40 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E48" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" t="s">
         <v>176</v>
-      </c>
-      <c r="F48" t="s">
-        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>865</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="O48" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="M48" s="25" t="s">
-        <v>868</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="O48" s="12" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -5516,19 +5558,19 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C49" t="s">
         <v>24</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E49">
         <v>1816</v>
       </c>
       <c r="F49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G49" s="6">
         <v>45865</v>
@@ -5537,22 +5579,22 @@
         <v>74</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>866</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O49" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M49" s="25" t="s">
-        <v>869</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O49" s="12" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5560,40 +5602,40 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C50" t="s">
         <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E50">
         <v>1820</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M50" s="25" t="s">
-        <v>870</v>
+        <v>544</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>867</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="O50" s="12" t="s">
-        <v>188</v>
+        <v>531</v>
+      </c>
+      <c r="O50" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -5601,40 +5643,40 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
         <v>24</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F51" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M51" s="25" t="s">
-        <v>871</v>
+        <v>544</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>868</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O51" s="12" t="s">
-        <v>192</v>
+        <v>529</v>
+      </c>
+      <c r="O51" s="8" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -5642,19 +5684,19 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C52" t="s">
         <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E52">
         <v>1767</v>
       </c>
       <c r="F52" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G52" s="6">
         <v>45763</v>
@@ -5663,22 +5705,22 @@
         <v>74</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M52" s="25" t="s">
-        <v>872</v>
+        <v>544</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>869</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O52" s="12" t="s">
-        <v>196</v>
+        <v>529</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="259.2" x14ac:dyDescent="0.3">
@@ -5686,40 +5728,40 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E53">
         <v>1813</v>
       </c>
       <c r="F53" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M53" s="25" t="s">
-        <v>873</v>
+        <v>544</v>
+      </c>
+      <c r="M53" s="20" t="s">
+        <v>870</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O53" s="12" t="s">
-        <v>200</v>
+        <v>526</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -5727,19 +5769,19 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E54">
         <v>1812</v>
       </c>
       <c r="F54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G54" s="6">
         <v>45714</v>
@@ -5748,22 +5790,22 @@
         <v>74</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="M54" s="25" t="s">
-        <v>875</v>
+        <v>549</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>872</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O54" s="12" t="s">
-        <v>204</v>
+        <v>529</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5771,19 +5813,19 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C55" t="s">
         <v>24</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E55">
         <v>1822</v>
       </c>
       <c r="F55" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G55" s="6">
         <v>45747</v>
@@ -5792,22 +5834,22 @@
         <v>74</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="M55" s="25" t="s">
-        <v>876</v>
+        <v>549</v>
+      </c>
+      <c r="M55" s="20" t="s">
+        <v>873</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O55" s="12" t="s">
-        <v>207</v>
+        <v>526</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5815,19 +5857,19 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E56">
         <v>1815</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G56" s="6">
         <v>45931</v>
@@ -5836,22 +5878,22 @@
         <v>74</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M56" s="25" t="s">
-        <v>877</v>
+        <v>544</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>874</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O56" s="12" t="s">
-        <v>211</v>
+        <v>529</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -5859,40 +5901,40 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C57" t="s">
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E57">
         <v>1830</v>
       </c>
       <c r="F57" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="M57" s="25" t="s">
-        <v>879</v>
+        <v>546</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>876</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="O57" s="12" t="s">
-        <v>215</v>
+        <v>607</v>
+      </c>
+      <c r="O57" s="8" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -5900,13 +5942,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C58" t="s">
         <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E58">
         <v>1833</v>
@@ -5915,22 +5957,22 @@
         <v>74</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M58" s="25" t="s">
-        <v>878</v>
+        <v>544</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>875</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O58" s="12" t="s">
-        <v>218</v>
+        <v>526</v>
+      </c>
+      <c r="O58" s="8" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -5938,43 +5980,43 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C59" t="s">
         <v>24</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E59">
         <v>1816</v>
       </c>
       <c r="F59" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I59" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M59" s="25" t="s">
-        <v>880</v>
+        <v>544</v>
+      </c>
+      <c r="M59" s="20" t="s">
+        <v>877</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O59" s="12" t="s">
-        <v>222</v>
+        <v>526</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -5982,43 +6024,43 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F60" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I60" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="M60" s="25" t="s">
-        <v>881</v>
+        <v>550</v>
+      </c>
+      <c r="M60" s="20" t="s">
+        <v>878</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O60" s="12" t="s">
-        <v>225</v>
+        <v>526</v>
+      </c>
+      <c r="O60" s="8" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6026,40 +6068,40 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C61" t="s">
         <v>24</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E61">
         <v>1837</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="M61" s="25" t="s">
-        <v>883</v>
+        <v>550</v>
+      </c>
+      <c r="M61" s="20" t="s">
+        <v>880</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O61" s="12" t="s">
-        <v>229</v>
+        <v>526</v>
+      </c>
+      <c r="O61" s="8" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -6067,37 +6109,37 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C62" t="s">
         <v>24</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="M62" s="25" t="s">
-        <v>884</v>
+        <v>551</v>
+      </c>
+      <c r="M62" s="20" t="s">
+        <v>881</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O62" s="12" t="s">
-        <v>232</v>
+        <v>526</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6105,13 +6147,13 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C63" t="s">
         <v>24</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E63">
         <v>1813</v>
@@ -6120,22 +6162,22 @@
         <v>74</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M63" s="25" t="s">
-        <v>885</v>
+        <v>544</v>
+      </c>
+      <c r="M63" s="20" t="s">
+        <v>882</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O63" s="12" t="s">
-        <v>207</v>
+        <v>526</v>
+      </c>
+      <c r="O63" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6143,40 +6185,40 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C64" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M64" s="25" t="s">
-        <v>886</v>
+        <v>544</v>
+      </c>
+      <c r="M64" s="20" t="s">
+        <v>883</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O64" s="12" t="s">
-        <v>804</v>
+        <v>526</v>
+      </c>
+      <c r="O64" s="8" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -6184,13 +6226,13 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C65" t="s">
         <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E65">
         <v>1818</v>
@@ -6202,25 +6244,25 @@
         <v>74</v>
       </c>
       <c r="I65" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M65" s="25" t="s">
-        <v>887</v>
+        <v>544</v>
+      </c>
+      <c r="M65" s="20" t="s">
+        <v>884</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O65" s="12" t="s">
-        <v>805</v>
+        <v>526</v>
+      </c>
+      <c r="O65" s="8" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6228,19 +6270,19 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
         <v>24</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G66" s="6">
         <v>45866</v>
@@ -6249,22 +6291,22 @@
         <v>74</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M66" s="25" t="s">
-        <v>888</v>
+        <v>544</v>
+      </c>
+      <c r="M66" s="20" t="s">
+        <v>885</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O66" s="12" t="s">
-        <v>240</v>
+        <v>529</v>
+      </c>
+      <c r="O66" s="8" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -6272,19 +6314,19 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E67">
         <v>1829</v>
       </c>
       <c r="F67" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G67" s="6">
         <v>45881</v>
@@ -6293,22 +6335,22 @@
         <v>74</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M67" s="25" t="s">
-        <v>889</v>
+        <v>544</v>
+      </c>
+      <c r="M67" s="20" t="s">
+        <v>886</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O67" s="12" t="s">
-        <v>806</v>
+        <v>526</v>
+      </c>
+      <c r="O67" s="8" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6316,40 +6358,40 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E68">
         <v>1818</v>
       </c>
       <c r="F68" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M68" s="25" t="s">
-        <v>890</v>
+        <v>544</v>
+      </c>
+      <c r="M68" s="20" t="s">
+        <v>887</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O68" s="23" t="s">
-        <v>807</v>
+        <v>526</v>
+      </c>
+      <c r="O68" s="19" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -6357,13 +6399,13 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C69" t="s">
         <v>24</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E69">
         <v>1814</v>
@@ -6372,22 +6414,22 @@
         <v>74</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="M69" s="25" t="s">
-        <v>891</v>
+        <v>583</v>
+      </c>
+      <c r="M69" s="20" t="s">
+        <v>888</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O69" s="12" t="s">
-        <v>252</v>
+        <v>526</v>
+      </c>
+      <c r="O69" s="8" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6395,40 +6437,40 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C70" t="s">
         <v>24</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E70">
         <v>1818</v>
       </c>
       <c r="F70" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M70" s="25" t="s">
-        <v>892</v>
+        <v>544</v>
+      </c>
+      <c r="M70" s="20" t="s">
+        <v>889</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O70" s="12" t="s">
-        <v>256</v>
+        <v>526</v>
+      </c>
+      <c r="O70" s="8" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -6436,13 +6478,13 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s">
         <v>24</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E71">
         <v>1820</v>
@@ -6451,22 +6493,22 @@
         <v>74</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="M71" s="25" t="s">
-        <v>867</v>
+        <v>584</v>
+      </c>
+      <c r="M71" s="20" t="s">
+        <v>864</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="O71" s="12" t="s">
-        <v>259</v>
+        <v>493</v>
+      </c>
+      <c r="O71" s="8" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6474,37 +6516,37 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="M72" s="25" t="s">
-        <v>894</v>
+        <v>585</v>
+      </c>
+      <c r="M72" s="20" t="s">
+        <v>891</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O72" s="12" t="s">
-        <v>262</v>
+        <v>526</v>
+      </c>
+      <c r="O72" s="8" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
@@ -6512,40 +6554,40 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E73">
         <v>1816</v>
       </c>
       <c r="F73" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M73" s="25" t="s">
-        <v>893</v>
+        <v>544</v>
+      </c>
+      <c r="M73" s="20" t="s">
+        <v>890</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O73" s="12" t="s">
-        <v>266</v>
+        <v>526</v>
+      </c>
+      <c r="O73" s="8" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6553,13 +6595,13 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E74">
         <v>1816</v>
@@ -6568,22 +6610,22 @@
         <v>74</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="M74" s="25" t="s">
-        <v>895</v>
+        <v>587</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>892</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O74" s="12" t="s">
-        <v>269</v>
+        <v>526</v>
+      </c>
+      <c r="O74" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6591,13 +6633,13 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E75">
         <v>1815</v>
@@ -6606,22 +6648,22 @@
         <v>74</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="M75" s="25" t="s">
-        <v>896</v>
+        <v>588</v>
+      </c>
+      <c r="M75" s="20" t="s">
+        <v>893</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O75" s="12" t="s">
-        <v>272</v>
+        <v>526</v>
+      </c>
+      <c r="O75" s="8" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -6629,40 +6671,40 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E76">
         <v>1815</v>
       </c>
       <c r="F76" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="M76" s="25" t="s">
-        <v>897</v>
+        <v>552</v>
+      </c>
+      <c r="M76" s="20" t="s">
+        <v>894</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O76" s="12" t="s">
-        <v>276</v>
+        <v>526</v>
+      </c>
+      <c r="O76" s="8" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -6670,37 +6712,37 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="M77" s="25" t="s">
-        <v>898</v>
+        <v>589</v>
+      </c>
+      <c r="M77" s="20" t="s">
+        <v>895</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O77" s="12" t="s">
-        <v>279</v>
+        <v>526</v>
+      </c>
+      <c r="O77" s="8" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -6708,19 +6750,19 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E78">
         <v>1813</v>
       </c>
       <c r="F78" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G78" s="6">
         <v>45935</v>
@@ -6729,22 +6771,22 @@
         <v>74</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="M78" s="26" t="s">
-        <v>899</v>
+        <v>590</v>
+      </c>
+      <c r="M78" s="20" t="s">
+        <v>896</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O78" s="12" t="s">
-        <v>283</v>
+        <v>526</v>
+      </c>
+      <c r="O78" s="8" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -6752,19 +6794,19 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E79">
         <v>1813</v>
       </c>
       <c r="F79" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G79" s="6">
         <v>45944</v>
@@ -6773,22 +6815,22 @@
         <v>74</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="M79" s="26" t="s">
-        <v>900</v>
+        <v>592</v>
+      </c>
+      <c r="M79" s="20" t="s">
+        <v>897</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O79" s="12" t="s">
-        <v>287</v>
+        <v>529</v>
+      </c>
+      <c r="O79" s="8" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
@@ -6796,19 +6838,19 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E80">
         <v>1815</v>
       </c>
       <c r="F80" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G80" s="6">
         <v>45720</v>
@@ -6817,22 +6859,22 @@
         <v>74</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="M80" s="26" t="s">
-        <v>901</v>
+        <v>591</v>
+      </c>
+      <c r="M80" s="20" t="s">
+        <v>898</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O80" s="12" t="s">
-        <v>291</v>
+        <v>529</v>
+      </c>
+      <c r="O80" s="8" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -6840,19 +6882,19 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E81">
         <v>1838</v>
       </c>
       <c r="F81" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G81" s="6">
         <v>45818</v>
@@ -6861,22 +6903,22 @@
         <v>74</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="M81" s="26" t="s">
-        <v>902</v>
+        <v>591</v>
+      </c>
+      <c r="M81" s="20" t="s">
+        <v>899</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O81" s="12" t="s">
-        <v>295</v>
+        <v>529</v>
+      </c>
+      <c r="O81" s="8" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="360" x14ac:dyDescent="0.3">
@@ -6884,19 +6926,19 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E82">
         <v>1816</v>
       </c>
       <c r="F82" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G82" s="6">
         <v>45864</v>
@@ -6905,22 +6947,22 @@
         <v>74</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="M82" s="26" t="s">
-        <v>903</v>
+        <v>591</v>
+      </c>
+      <c r="M82" s="20" t="s">
+        <v>900</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O82" s="12" t="s">
-        <v>299</v>
+        <v>529</v>
+      </c>
+      <c r="O82" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -6928,13 +6970,13 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E83">
         <v>1820</v>
@@ -6943,22 +6985,22 @@
         <v>74</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="M83" s="26" t="s">
-        <v>904</v>
+        <v>591</v>
+      </c>
+      <c r="M83" s="20" t="s">
+        <v>901</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="O83" s="12" t="s">
-        <v>302</v>
+        <v>605</v>
+      </c>
+      <c r="O83" s="8" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
@@ -6966,19 +7008,19 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E84">
         <v>1802</v>
       </c>
       <c r="F84" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G84" s="6">
         <v>45946</v>
@@ -6987,22 +7029,22 @@
         <v>74</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M84" s="26" t="s">
-        <v>907</v>
+        <v>544</v>
+      </c>
+      <c r="M84" s="20" t="s">
+        <v>904</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O84" s="12" t="s">
-        <v>306</v>
+        <v>526</v>
+      </c>
+      <c r="O84" s="8" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -7010,19 +7052,19 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E85">
         <v>1802</v>
       </c>
       <c r="F85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G85" s="6">
         <v>45793</v>
@@ -7031,22 +7073,22 @@
         <v>74</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M85" s="26" t="s">
-        <v>908</v>
+        <v>547</v>
+      </c>
+      <c r="M85" s="20" t="s">
+        <v>905</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O85" s="12" t="s">
-        <v>310</v>
+        <v>526</v>
+      </c>
+      <c r="O85" s="8" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -7054,37 +7096,37 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M86" s="26" t="s">
-        <v>905</v>
+        <v>547</v>
+      </c>
+      <c r="M86" s="20" t="s">
+        <v>902</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O86" s="12" t="s">
-        <v>313</v>
+        <v>526</v>
+      </c>
+      <c r="O86" s="8" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -7092,37 +7134,37 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E87" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="M87" s="26" t="s">
-        <v>906</v>
+        <v>593</v>
+      </c>
+      <c r="M87" s="20" t="s">
+        <v>903</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O87" s="12" t="s">
-        <v>316</v>
+        <v>526</v>
+      </c>
+      <c r="O87" s="8" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -7130,37 +7172,37 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E88" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="M88" s="26" t="s">
-        <v>909</v>
+        <v>553</v>
+      </c>
+      <c r="M88" s="20" t="s">
+        <v>906</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O88" s="12" t="s">
-        <v>320</v>
+        <v>526</v>
+      </c>
+      <c r="O88" s="8" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
@@ -7168,19 +7210,19 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E89">
         <v>1804</v>
       </c>
       <c r="F89" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G89" s="6">
         <v>46364</v>
@@ -7189,25 +7231,25 @@
         <v>74</v>
       </c>
       <c r="I89" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="M89" s="26" t="s">
-        <v>910</v>
+        <v>590</v>
+      </c>
+      <c r="M89" s="20" t="s">
+        <v>907</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O89" s="12" t="s">
-        <v>324</v>
+        <v>526</v>
+      </c>
+      <c r="O89" s="8" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
@@ -7215,43 +7257,43 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E90">
         <v>1802</v>
       </c>
       <c r="F90" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G90" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="M90" s="26" t="s">
-        <v>911</v>
+        <v>547</v>
+      </c>
+      <c r="M90" s="20" t="s">
+        <v>908</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O90" s="12" t="s">
-        <v>328</v>
+        <v>526</v>
+      </c>
+      <c r="O90" s="8" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
@@ -7259,37 +7301,37 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E91" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="M91" s="26" t="s">
-        <v>912</v>
+        <v>590</v>
+      </c>
+      <c r="M91" s="20" t="s">
+        <v>909</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O91" s="12" t="s">
-        <v>331</v>
+        <v>526</v>
+      </c>
+      <c r="O91" s="8" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
@@ -7297,43 +7339,43 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E92" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F92" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I92" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="M92" s="26" t="s">
-        <v>913</v>
+        <v>594</v>
+      </c>
+      <c r="M92" s="20" t="s">
+        <v>910</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O92" s="12" t="s">
-        <v>334</v>
+        <v>526</v>
+      </c>
+      <c r="O92" s="8" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -7341,40 +7383,40 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F93" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M93" s="26" t="s">
-        <v>914</v>
+        <v>595</v>
+      </c>
+      <c r="M93" s="20" t="s">
+        <v>911</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O93" s="12" t="s">
-        <v>338</v>
+        <v>526</v>
+      </c>
+      <c r="O93" s="8" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
@@ -7382,40 +7424,40 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="M94" s="26" t="s">
-        <v>915</v>
+        <v>596</v>
+      </c>
+      <c r="M94" s="20" t="s">
+        <v>912</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O94" s="12" t="s">
-        <v>341</v>
+        <v>529</v>
+      </c>
+      <c r="O94" s="8" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
@@ -7423,37 +7465,37 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M95" s="26" t="s">
-        <v>916</v>
+        <v>595</v>
+      </c>
+      <c r="M95" s="20" t="s">
+        <v>913</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O95" s="12" t="s">
-        <v>344</v>
+        <v>526</v>
+      </c>
+      <c r="O95" s="8" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="288" x14ac:dyDescent="0.3">
@@ -7461,19 +7503,19 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E96">
         <v>1801</v>
       </c>
       <c r="F96" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G96" s="6">
         <v>45989</v>
@@ -7482,22 +7524,22 @@
         <v>74</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M96" s="26" t="s">
-        <v>917</v>
+        <v>595</v>
+      </c>
+      <c r="M96" s="20" t="s">
+        <v>914</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O96" s="12" t="s">
-        <v>348</v>
+        <v>529</v>
+      </c>
+      <c r="O96" s="8" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -7505,43 +7547,43 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E97">
         <v>1801</v>
       </c>
       <c r="F97" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G97" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M97" s="26" t="s">
-        <v>918</v>
+        <v>595</v>
+      </c>
+      <c r="M97" s="20" t="s">
+        <v>915</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O97" s="12" t="s">
-        <v>353</v>
+        <v>529</v>
+      </c>
+      <c r="O97" s="8" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
@@ -7549,19 +7591,19 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F98" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G98" s="6">
         <v>45729</v>
@@ -7570,77 +7612,77 @@
         <v>74</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="M98" s="26" t="s">
-        <v>919</v>
+        <v>596</v>
+      </c>
+      <c r="M98" s="20" t="s">
+        <v>916</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="O98" s="12" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+      <c r="O98" s="8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F99" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>76</v>
+        <v>596</v>
+      </c>
+      <c r="M99" s="20" t="s">
+        <v>917</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="O99" s="12" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+      <c r="O99" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="360" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E100">
         <v>1802</v>
@@ -7652,408 +7694,408 @@
         <v>74</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>76</v>
+        <v>595</v>
+      </c>
+      <c r="M100" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O100" s="12" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O100" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E101">
         <v>1802</v>
       </c>
       <c r="F101" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="M101" s="1" t="s">
-        <v>76</v>
+        <v>597</v>
+      </c>
+      <c r="M101" s="20" t="s">
+        <v>918</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O101" s="12" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O101" s="8" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="360" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E102" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F102" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>76</v>
+        <v>598</v>
+      </c>
+      <c r="M102" s="20" t="s">
+        <v>920</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O102" s="12" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="O102" s="8" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E103" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F103" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>76</v>
+        <v>599</v>
+      </c>
+      <c r="M103" s="20" t="s">
+        <v>921</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O103" s="12" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="O103" s="8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F104" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M104" s="1" t="s">
-        <v>76</v>
+        <v>595</v>
+      </c>
+      <c r="M104" s="20" t="s">
+        <v>922</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O104" s="12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O104" s="8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E105" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F105" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M105" s="1" t="s">
-        <v>76</v>
+        <v>595</v>
+      </c>
+      <c r="M105" s="20" t="s">
+        <v>923</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O105" s="12" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="O105" s="8" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E106" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F106" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>76</v>
+        <v>599</v>
+      </c>
+      <c r="M106" s="20" t="s">
+        <v>924</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O106" s="12" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="O106" s="8" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E107">
         <v>1802</v>
       </c>
       <c r="F107" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M107" s="1" t="s">
-        <v>76</v>
+        <v>595</v>
+      </c>
+      <c r="M107" s="20" t="s">
+        <v>925</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O107" s="12" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O107" s="8" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E108" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="M108" s="1" t="s">
-        <v>76</v>
+        <v>599</v>
+      </c>
+      <c r="M108" s="20" t="s">
+        <v>926</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O108" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O108" s="8" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E109" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F109" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="M109" s="1" t="s">
-        <v>76</v>
+        <v>595</v>
+      </c>
+      <c r="M109" s="20" t="s">
+        <v>927</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="O109" s="12" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+      <c r="O109" s="8" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E110">
         <v>1807</v>
       </c>
       <c r="F110" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G110" s="6">
         <v>45763</v>
@@ -8062,121 +8104,121 @@
         <v>74</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>76</v>
+        <v>600</v>
+      </c>
+      <c r="M110" s="20" t="s">
+        <v>928</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="O110" s="12" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+      <c r="O110" s="8" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>76</v>
+        <v>601</v>
+      </c>
+      <c r="M111" s="20" t="s">
+        <v>929</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="O111" s="12" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+      <c r="O111" s="8" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E112" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F112" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="M112" s="1" t="s">
-        <v>76</v>
+        <v>601</v>
+      </c>
+      <c r="M112" s="20" t="s">
+        <v>930</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="O112" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+      <c r="O112" s="8" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E113" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F113" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G113" s="6">
         <v>45840</v>
@@ -8185,118 +8227,118 @@
         <v>74</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>76</v>
+        <v>602</v>
+      </c>
+      <c r="M113" s="20" t="s">
+        <v>931</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="O113" s="12" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+      <c r="O113" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E114" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>76</v>
+        <v>603</v>
+      </c>
+      <c r="M114" s="20" t="s">
+        <v>932</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="O114" s="12" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+      <c r="O114" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E115" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>76</v>
+        <v>604</v>
+      </c>
+      <c r="M115" s="20" t="s">
+        <v>933</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="O115" s="12" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+      <c r="O115" s="8" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E116">
         <v>1812</v>
       </c>
       <c r="F116" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G116" s="6">
         <v>45802</v>
@@ -8305,39 +8347,39 @@
         <v>74</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>76</v>
+        <v>604</v>
+      </c>
+      <c r="M116" s="20" t="s">
+        <v>934</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E117" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G117" s="6">
         <v>45692</v>
@@ -8346,42 +8388,42 @@
         <v>74</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="M117" s="1" t="s">
-        <v>76</v>
+        <v>574</v>
+      </c>
+      <c r="M117" s="20" t="s">
+        <v>935</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E118">
         <v>1818</v>
       </c>
       <c r="F118" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G118" s="6">
         <v>45893</v>
@@ -8390,63 +8432,63 @@
         <v>74</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="M118" s="1" t="s">
-        <v>76</v>
+        <v>590</v>
+      </c>
+      <c r="M118" s="20" t="s">
+        <v>936</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E119">
         <v>1802</v>
       </c>
       <c r="F119" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>76</v>
+        <v>599</v>
+      </c>
+      <c r="M119" s="20" t="s">
+        <v>937</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -8477,11 +8519,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>584</v>
+      <c r="A2" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -8489,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8497,7 +8539,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8505,7 +8547,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8513,7 +8555,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8521,7 +8563,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -8529,7 +8571,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8537,7 +8579,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -8545,7 +8587,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8553,7 +8595,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8561,7 +8603,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -8569,7 +8611,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -8577,7 +8619,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -8587,12 +8629,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="130.21875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="130.21875" style="17" customWidth="1"/>
     <col min="4" max="4" width="78.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="100.77734375" style="1" customWidth="1"/>
   </cols>
@@ -8604,14 +8646,14 @@
       <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>616</v>
+      <c r="C1" s="15" t="s">
+        <v>614</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8621,14 +8663,14 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>614</v>
+      <c r="C2" s="16" t="s">
+        <v>612</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8775,11 +8817,11 @@
       <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="22" t="s">
-        <v>618</v>
+      <c r="C21" s="18" t="s">
+        <v>616</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
@@ -8789,11 +8831,11 @@
       <c r="B22" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="22" t="s">
-        <v>619</v>
+      <c r="C22" s="18" t="s">
+        <v>617</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -8801,13 +8843,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -8815,13 +8857,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>622</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>621</v>
+        <v>82</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>620</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -8829,22 +8871,22 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="22"/>
+        <v>88</v>
+      </c>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:5" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>627</v>
+        <v>91</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>625</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
@@ -8852,16 +8894,16 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>624</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>623</v>
+        <v>95</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>622</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>621</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -8869,13 +8911,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>625</v>
+        <v>99</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>623</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
@@ -8883,13 +8925,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>626</v>
+        <v>103</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>624</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="192" customHeight="1" x14ac:dyDescent="0.3">
@@ -8897,13 +8939,13 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>628</v>
+        <v>107</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>626</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="124.8" x14ac:dyDescent="0.3">
@@ -8911,13 +8953,13 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>629</v>
+        <v>111</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -8925,13 +8967,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>630</v>
+        <v>115</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>628</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -8939,13 +8981,13 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>631</v>
+        <v>119</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>629</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -8953,10 +8995,10 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>632</v>
+        <v>123</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -8964,16 +9006,16 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>633</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>815</v>
+        <v>127</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>812</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -8981,7 +9023,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -8989,13 +9031,13 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>634</v>
+        <v>134</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>632</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -9003,7 +9045,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -9011,13 +9053,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>635</v>
+        <v>141</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>633</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -9025,13 +9067,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>636</v>
+        <v>145</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>634</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -9039,13 +9081,13 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>637</v>
+        <v>148</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>635</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -9053,13 +9095,13 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>638</v>
+        <v>151</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>636</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -9067,10 +9109,10 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>639</v>
+        <v>155</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
@@ -9078,13 +9120,13 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>640</v>
+        <v>159</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>638</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
@@ -9092,13 +9134,13 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>784</v>
+        <v>162</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>781</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
@@ -9106,13 +9148,13 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>641</v>
+        <v>166</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>639</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -9120,7 +9162,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -9128,10 +9170,10 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>642</v>
+        <v>174</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -9139,968 +9181,957 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
-      </c>
-      <c r="C49" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>183</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>187</v>
+      </c>
+      <c r="C51" t="s">
         <v>643</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>50</v>
-      </c>
-      <c r="B50" t="s">
-        <v>184</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>51</v>
-      </c>
-      <c r="B51" t="s">
-        <v>185</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>645</v>
+      <c r="E51" s="1" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C52" t="s">
+        <v>644</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>54</v>
+      </c>
+      <c r="B53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C54" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>53</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53" t="s">
-        <v>647</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>54</v>
-      </c>
-      <c r="B54" t="s">
-        <v>197</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>648</v>
+      <c r="E54" s="1" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>210</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>649</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>56</v>
-      </c>
-      <c r="B56" t="s">
-        <v>205</v>
-      </c>
-      <c r="C56" s="22" t="s">
+      <c r="D57" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>214</v>
+      </c>
+      <c r="D58" s="13" t="s">
         <v>650</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>57</v>
-      </c>
-      <c r="B57" t="s">
-        <v>208</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>790</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>58</v>
-      </c>
-      <c r="B58" t="s">
-        <v>212</v>
-      </c>
-      <c r="C58" s="22" t="s">
+    </row>
+    <row r="59" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>221</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>652</v>
       </c>
-      <c r="D58" s="17" t="s">
-        <v>651</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>59</v>
-      </c>
-      <c r="B59" t="s">
-        <v>216</v>
-      </c>
-      <c r="D59" s="17" t="s">
+    </row>
+    <row r="61" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>224</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>60</v>
-      </c>
-      <c r="B60" t="s">
-        <v>219</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>61</v>
-      </c>
-      <c r="B61" t="s">
-        <v>223</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>226</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>656</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C64" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>235</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>658</v>
+        <v>236</v>
+      </c>
+      <c r="C65" t="s">
+        <v>657</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>698</v>
+        <v>788</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>238</v>
-      </c>
-      <c r="C66" t="s">
+        <v>239</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>532</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>659</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="D68" s="13" t="s">
         <v>660</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>67</v>
-      </c>
-      <c r="B67" t="s">
-        <v>241</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>661</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>68</v>
-      </c>
-      <c r="B68" t="s">
-        <v>534</v>
-      </c>
-      <c r="C68" s="22" t="s">
+      <c r="E68" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>70</v>
+      </c>
+      <c r="B69" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70" t="s">
+        <v>251</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>663</v>
+      </c>
+      <c r="D70" s="13" t="s">
         <v>662</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>69</v>
-      </c>
-      <c r="B69" t="s">
-        <v>246</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>664</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>663</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>70</v>
-      </c>
-      <c r="B70" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E70" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>253</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>666</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>665</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>701</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>260</v>
-      </c>
-      <c r="D73" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>75</v>
+      </c>
+      <c r="B74" t="s">
+        <v>265</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>667</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>74</v>
-      </c>
-      <c r="B74" t="s">
-        <v>263</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>669</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>668</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>267</v>
-      </c>
-      <c r="D75" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
+        <v>271</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>76</v>
-      </c>
-      <c r="B76" t="s">
-        <v>270</v>
-      </c>
-      <c r="C76" s="21" t="s">
+      <c r="E76" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>78</v>
+      </c>
+      <c r="B77" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
+        <v>278</v>
+      </c>
+      <c r="C78" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="D76" s="17" t="s">
-        <v>671</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>80</v>
+      </c>
+      <c r="B79" t="s">
+        <v>282</v>
+      </c>
+      <c r="C79" s="17" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>77</v>
-      </c>
-      <c r="B77" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>674</v>
-      </c>
-      <c r="D77" s="17" t="s">
-        <v>673</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="E79" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" s="18" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>78</v>
-      </c>
-      <c r="B78" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>79</v>
-      </c>
-      <c r="B79" t="s">
-        <v>280</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>675</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>290</v>
+      </c>
+      <c r="C81" s="18" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>80</v>
-      </c>
-      <c r="B80" t="s">
-        <v>284</v>
-      </c>
-      <c r="C80" s="21" t="s">
+      <c r="E81" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>83</v>
+      </c>
+      <c r="B82" t="s">
+        <v>294</v>
+      </c>
+      <c r="C82" s="17" t="s">
         <v>706</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>81</v>
-      </c>
-      <c r="B81" t="s">
-        <v>288</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>707</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>82</v>
-      </c>
-      <c r="B82" t="s">
-        <v>292</v>
-      </c>
-      <c r="C82" s="22" t="s">
-        <v>708</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>296</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>709</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>303</v>
-      </c>
-      <c r="C85" s="22" t="s">
-        <v>710</v>
+        <v>305</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>708</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>748</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>311</v>
+        <v>312</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>314</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>709</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="78" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
-      </c>
-      <c r="C90" s="22" t="s">
-        <v>712</v>
+        <v>323</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="78" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>325</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>752</v>
+        <v>327</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>747</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>329</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>750</v>
-      </c>
-      <c r="E92" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>94</v>
+      </c>
+      <c r="B93" t="s">
+        <v>333</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>710</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>93</v>
-      </c>
-      <c r="B93" t="s">
-        <v>332</v>
-      </c>
-      <c r="D93" s="17" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>335</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>713</v>
+        <v>337</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>711</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>339</v>
-      </c>
-      <c r="C95" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>97</v>
+      </c>
+      <c r="B96" t="s">
+        <v>343</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>347</v>
+      </c>
+      <c r="C97" s="18" t="s">
         <v>714</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>96</v>
-      </c>
-      <c r="B96" t="s">
-        <v>342</v>
-      </c>
-      <c r="C96" s="21" t="s">
+    <row r="98" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>99</v>
+      </c>
+      <c r="B98" t="s">
+        <v>352</v>
+      </c>
+      <c r="C98" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>97</v>
-      </c>
-      <c r="B97" t="s">
-        <v>345</v>
-      </c>
-      <c r="C97" s="21" t="s">
+    <row r="99" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>100</v>
+      </c>
+      <c r="B99" t="s">
+        <v>356</v>
+      </c>
+      <c r="C99" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>98</v>
-      </c>
-      <c r="B98" t="s">
-        <v>349</v>
-      </c>
-      <c r="C98" s="22" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>360</v>
+      </c>
+      <c r="C100" s="17" t="s">
         <v>717</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>99</v>
-      </c>
-      <c r="B99" t="s">
-        <v>354</v>
-      </c>
-      <c r="C99" s="22" t="s">
+    <row r="101" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>102</v>
+      </c>
+      <c r="B101" t="s">
+        <v>363</v>
+      </c>
+      <c r="C101" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>100</v>
-      </c>
-      <c r="B100" t="s">
-        <v>358</v>
-      </c>
-      <c r="C100" s="22" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>103</v>
+      </c>
+      <c r="B102" t="s">
+        <v>367</v>
+      </c>
+      <c r="C102" s="17" t="s">
         <v>719</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>101</v>
-      </c>
-      <c r="B101" t="s">
-        <v>362</v>
-      </c>
-      <c r="C101" s="21" t="s">
+    <row r="103" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>104</v>
+      </c>
+      <c r="B103" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="18" t="s">
         <v>720</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="D103" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>102</v>
-      </c>
-      <c r="B102" t="s">
-        <v>365</v>
-      </c>
-      <c r="C102" s="22" t="s">
+    <row r="104" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
+        <v>374</v>
+      </c>
+      <c r="C104" s="17" t="s">
         <v>721</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="D104" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>103</v>
-      </c>
-      <c r="B103" t="s">
-        <v>369</v>
-      </c>
-      <c r="C103" s="21" t="s">
+    <row r="105" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>106</v>
+      </c>
+      <c r="B105" t="s">
+        <v>378</v>
+      </c>
+      <c r="C105" s="18" t="s">
         <v>722</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="D105" s="13" t="s">
+        <v>725</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>104</v>
-      </c>
-      <c r="B104" t="s">
-        <v>372</v>
-      </c>
-      <c r="C104" s="22" t="s">
+    <row r="106" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
+        <v>381</v>
+      </c>
+      <c r="C106" s="18" t="s">
         <v>723</v>
       </c>
-      <c r="D104" s="17" t="s">
-        <v>678</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="D106" s="13" t="s">
+        <v>724</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>105</v>
-      </c>
-      <c r="B105" t="s">
-        <v>376</v>
-      </c>
-      <c r="C105" s="21" t="s">
-        <v>724</v>
-      </c>
-      <c r="D105" s="17" t="s">
-        <v>679</v>
-      </c>
-      <c r="E105" s="1" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>108</v>
+      </c>
+      <c r="B107" t="s">
+        <v>385</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>765</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>106</v>
-      </c>
-      <c r="B106" t="s">
-        <v>380</v>
-      </c>
-      <c r="C106" s="22" t="s">
-        <v>725</v>
-      </c>
-      <c r="D106" s="17" t="s">
-        <v>728</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>107</v>
-      </c>
-      <c r="B107" t="s">
-        <v>383</v>
-      </c>
-      <c r="C107" s="22" t="s">
-        <v>726</v>
-      </c>
-      <c r="D107" s="17" t="s">
-        <v>727</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>387</v>
-      </c>
-      <c r="C108" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="C108" s="17" t="s">
         <v>729</v>
       </c>
-      <c r="D108" s="17" t="s">
-        <v>730</v>
+      <c r="D108" s="1" t="s">
+        <v>728</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
         <v>390</v>
       </c>
-      <c r="C109" s="21" t="s">
-        <v>732</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>731</v>
+      <c r="C109" s="17" t="s">
+        <v>730</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
         <v>392</v>
       </c>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>395</v>
+      </c>
+      <c r="C111" s="18" t="s">
         <v>733</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>111</v>
-      </c>
-      <c r="B111" t="s">
-        <v>394</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>734</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>735</v>
+      <c r="D111" s="13" t="s">
+        <v>732</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B112" t="s">
         <v>397</v>
       </c>
-      <c r="C112" s="22" t="s">
+      <c r="C112" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="D112" s="14" t="s">
+        <v>734</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>114</v>
+      </c>
+      <c r="B113" t="s">
+        <v>400</v>
+      </c>
+      <c r="C113" s="18" t="s">
         <v>736</v>
       </c>
-      <c r="D112" s="17" t="s">
-        <v>735</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>113</v>
-      </c>
-      <c r="B113" t="s">
-        <v>399</v>
-      </c>
-      <c r="C113" s="21" t="s">
-        <v>738</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>737</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>402</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>739</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>774</v>
+        <v>404</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="C116" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>411</v>
-      </c>
-      <c r="C117" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>119</v>
+      </c>
+      <c r="B118" t="s">
+        <v>416</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>739</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>120</v>
+      </c>
+      <c r="B119" t="s">
+        <v>419</v>
+      </c>
+      <c r="C119" s="18" t="s">
         <v>740</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>775</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <v>118</v>
-      </c>
-      <c r="B118" t="s">
-        <v>415</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>741</v>
-      </c>
-      <c r="D118" s="17" t="s">
-        <v>680</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <v>119</v>
-      </c>
-      <c r="B119" t="s">
-        <v>418</v>
-      </c>
-      <c r="C119" s="21" t="s">
-        <v>742</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <v>120</v>
-      </c>
-      <c r="B120" t="s">
-        <v>421</v>
-      </c>
-      <c r="C120" s="22" t="s">
-        <v>743</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -10119,12 +10150,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -10134,47 +10165,47 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
@@ -10184,12 +10215,12 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
@@ -10204,102 +10235,102 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
@@ -10309,242 +10340,242 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -10565,107 +10596,107 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
@@ -10675,27 +10706,27 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
